--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1D21EC-FCF4-4BF9-BAD3-C508A5CB1F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D32966-93DB-45BD-8F42-8C81CEC6AF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Дата1</t>
-  </si>
-  <si>
-    <t>Diary_SalesmanBotOpenSource</t>
   </si>
   <si>
     <t>апрель 2026.</t>
@@ -103,6 +100,18 @@
   </si>
   <si>
     <t>При изменении прайса чтобы можно было просто и быстро положить прайс в Excel в специальную папку, и чтобы чатбот тут же его увидел.</t>
+  </si>
+  <si>
+    <t>Может быть, спросить провайдера о причинах блокировки порта 443 ? Может ли он открыть порт 443 нам ?</t>
+  </si>
+  <si>
+    <t>25 мая 2026.</t>
+  </si>
+  <si>
+    <t>Должен ли чат бот что-либо знать о курсах валют ?</t>
+  </si>
+  <si>
+    <t>Diary_SalesmanBotOpenSource. Ход работы</t>
   </si>
 </sst>
 </file>
@@ -421,7 +430,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -441,14 +450,14 @@
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -457,11 +466,11 @@
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -470,47 +479,47 @@
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4409,7 +4418,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -4422,50 +4431,50 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4475,7 +4484,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B31E73-EC71-4EBC-A252-91C0E5847F41}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -4483,7 +4492,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -4496,19 +4505,36 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s">
-        <v>19</v>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>18</v>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K5" r:id="rId1" xr:uid="{2EFE727E-DCE9-4EBF-8555-EE77DB6C2AF6}"/>
   </hyperlinks>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D32966-93DB-45BD-8F42-8C81CEC6AF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA142D3A-628C-44EC-91C3-59BD8BF8E92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>Дата1</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>Diary_SalesmanBotOpenSource. Ход работы</t>
+  </si>
+  <si>
+    <t>Должен ли чат бот что-либо знать об остатках товаров ?</t>
   </si>
 </sst>
 </file>
@@ -4470,9 +4473,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="C10" t="s">
         <v>25</v>
       </c>
@@ -4484,7 +4485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B31E73-EC71-4EBC-A252-91C0E5847F41}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -4533,6 +4534,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA142D3A-628C-44EC-91C3-59BD8BF8E92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBB5D6E-A1C9-4D3F-BE4C-69266A690008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>Дата1</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Должен ли чат бот что-либо знать об остатках товаров ?</t>
+  </si>
+  <si>
+    <t>Если да, то должен ли он разделять остакти товаров по разным складам ?</t>
   </si>
 </sst>
 </file>
@@ -4485,7 +4488,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B31E73-EC71-4EBC-A252-91C0E5847F41}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -4542,6 +4545,11 @@
         <v>30</v>
       </c>
     </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBB5D6E-A1C9-4D3F-BE4C-69266A690008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71A21E7-5D61-4CF2-974E-9C3508FAC353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>Дата1</t>
   </si>
@@ -93,9 +93,6 @@
     <t>18 мая 2026.</t>
   </si>
   <si>
-    <t>Получается, чатбот дожен быть програамой около которой как от сердцевины должны работать коннекты к сервисам.</t>
-  </si>
-  <si>
     <t>Должно быть чтение чатботом прайм-листа который для клиентов, без утомительной переделки прайса специально под чатбота.</t>
   </si>
   <si>
@@ -118,6 +115,42 @@
   </si>
   <si>
     <t>Если да, то должен ли он разделять остакти товаров по разным складам ?</t>
+  </si>
+  <si>
+    <t>WB - разработка структуры прайс-листа, новые классы группы Price.</t>
+  </si>
+  <si>
+    <t>26 мая 2026.</t>
+  </si>
+  <si>
+    <t>От предприятия нужно перейти на прайс для клиентов, который будет также и одновременно автоматически разбираться чат-ботом.</t>
+  </si>
+  <si>
+    <t>Одна товарная группа прайса не должна разбиваться по разным колонкам прайса.</t>
+  </si>
+  <si>
+    <t>Должен ли чат бот что-либо знать о сортаменте ?</t>
+  </si>
+  <si>
+    <t>Если да, то как выглядит сортамент для чат бота, какие колонки, как с ними работать ?</t>
+  </si>
+  <si>
+    <t>Может быть, по аналогии с прайсом разработать общий расчетный лист для менеджеров и чат бота ?</t>
+  </si>
+  <si>
+    <t>Должен ли чат бот выполнять расчеты по сортаменту  (для клиентов, для менеджеров)  ?</t>
+  </si>
+  <si>
+    <t>Должен ли чат бот выполнять расчеты по объему работ (для клиентов, для менеджеров) ?</t>
+  </si>
+  <si>
+    <t>Должен ли чат бот выполнять расчеты по стандартным изделиям (пластины, закладные и т.д.) (для клиентов, для менеджеров) ?</t>
+  </si>
+  <si>
+    <t>Получается, чатбот дожен быть программой около которой как от сердцевины должны работать коннекты к сервисам.</t>
+  </si>
+  <si>
+    <t>Окультуривание общего вида проекта SMBOS, придание ему смысловой целостности, подготовка класса-шаблона и другой инфраструктуры.</t>
   </si>
 </sst>
 </file>
@@ -436,7 +469,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -529,12 +562,22 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="B14" s="3"/>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
+      <c r="A15" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="B15" s="3"/>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
@@ -4464,7 +4507,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -4472,13 +4515,15 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="C10" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4488,7 +4533,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B31E73-EC71-4EBC-A252-91C0E5847F41}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -4526,28 +4571,95 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
-        <v>31</v>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71A21E7-5D61-4CF2-974E-9C3508FAC353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885FC174-B66C-4931-B82E-169149A780ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>Дата1</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>Окультуривание общего вида проекта SMBOS, придание ему смысловой целостности, подготовка класса-шаблона и другой инфраструктуры.</t>
+  </si>
+  <si>
+    <t>SM - разработка поддерживающей инфрастуктуры. Выделение классов.</t>
   </si>
 </sst>
 </file>
@@ -580,70 +583,80 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
     </row>
-    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
-    <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
     </row>
-    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
     </row>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Мои док\_Мой рабстол\Новая папка\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885FC174-B66C-4931-B82E-169149A780ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A8B567-8989-404C-9108-69151EB858A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
   <si>
     <t>Дата1</t>
   </si>
@@ -114,9 +114,6 @@
     <t>Должен ли чат бот что-либо знать об остатках товаров ?</t>
   </si>
   <si>
-    <t>Если да, то должен ли он разделять остакти товаров по разным складам ?</t>
-  </si>
-  <si>
     <t>WB - разработка структуры прайс-листа, новые классы группы Price.</t>
   </si>
   <si>
@@ -154,6 +151,24 @@
   </si>
   <si>
     <t>SM - разработка поддерживающей инфрастуктуры. Выделение классов.</t>
+  </si>
+  <si>
+    <t>Если да, то должен ли он разделять остакти товаров по разным складам и\или разным филиалам ?</t>
+  </si>
+  <si>
+    <t>27 мая 2026.</t>
+  </si>
+  <si>
+    <t>28 мая 2026.</t>
+  </si>
+  <si>
+    <t>Почему-то пока не получается рассовать все скрипты и классы по разным папкам проекта - не работает, хоть ты тресни.</t>
+  </si>
+  <si>
+    <t>SM - функции и инструменты для цен перенесены из главного скрипта в pricelistengine.</t>
+  </si>
+  <si>
+    <t>SM - объекты Model, AgentParams выделены в отдельные классы из главного скрипта. Потом присоединены к классу Chat.</t>
   </si>
 </sst>
 </file>
@@ -570,7 +585,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -579,38 +594,53 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="B18" s="3"/>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="B19" s="3"/>
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
+      <c r="A20" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="B20" s="3"/>
+      <c r="C20" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
@@ -4520,7 +4550,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -4546,7 +4576,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B31E73-EC71-4EBC-A252-91C0E5847F41}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -4608,71 +4638,79 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Мои док\_Мой рабстол\Новая папка\SalesmanBotOpenSource\docu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A8B567-8989-404C-9108-69151EB858A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46B9FAA-6857-4BC5-94BB-0CFA1090EC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
   <si>
     <t>Дата1</t>
   </si>
@@ -162,13 +162,19 @@
     <t>28 мая 2026.</t>
   </si>
   <si>
+    <t>SM - объекты Model, AgentParams выделены в отдельные классы из главного скрипта.</t>
+  </si>
+  <si>
     <t>Почему-то пока не получается рассовать все скрипты и классы по разным папкам проекта - не работает, хоть ты тресни.</t>
   </si>
   <si>
     <t>SM - функции и инструменты для цен перенесены из главного скрипта в pricelistengine.</t>
   </si>
   <si>
-    <t>SM - объекты Model, AgentParams выделены в отдельные классы из главного скрипта. Потом присоединены к классу Chat.</t>
+    <t>29 мая 2026.</t>
+  </si>
+  <si>
+    <t>SM - укрупнение, переименование и упрощение модулей.</t>
   </si>
 </sst>
 </file>
@@ -630,7 +636,7 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -639,12 +645,17 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="B21" s="3"/>
+      <c r="C21" s="2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
@@ -4710,7 +4721,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46B9FAA-6857-4BC5-94BB-0CFA1090EC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E5FDE9-5CCE-4EEB-B2EC-8CC075BD5DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ход работы" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
   <si>
     <t>Дата1</t>
   </si>
@@ -93,9 +93,6 @@
     <t>18 мая 2026.</t>
   </si>
   <si>
-    <t>Должно быть чтение чатботом прайм-листа который для клиентов, без утомительной переделки прайса специально под чатбота.</t>
-  </si>
-  <si>
     <t>При изменении прайса чтобы можно было просто и быстро положить прайс в Excel в специальную папку, и чтобы чатбот тут же его увидел.</t>
   </si>
   <si>
@@ -175,13 +172,49 @@
   </si>
   <si>
     <t>SM - укрупнение, переименование и упрощение модулей.</t>
+  </si>
+  <si>
+    <t>Решено.</t>
+  </si>
+  <si>
+    <t>Нет, коннекта с телеграм не нужно.</t>
+  </si>
+  <si>
+    <t>Чат бот должен видеть остатки товаров в разрезе складов.</t>
+  </si>
+  <si>
+    <t>Решено - чат бот не должен видеть курсы валют, ему это не надо.</t>
+  </si>
+  <si>
+    <t>Должно быть чтение чатботом прайс-листа который для клиентов, без утомительной переделки прайса специально под чатбота.</t>
+  </si>
+  <si>
+    <t>30 мая 2026.</t>
+  </si>
+  <si>
+    <t>SM - перебор и тестирование GUI - tkinter, customTkinter, freeSimpleGUI, streamlit, dearPyGui.</t>
+  </si>
+  <si>
+    <t>Сможет ли чат бот выписать клиенту счет на оплату ?</t>
+  </si>
+  <si>
+    <t>Да, сможет, если ему будет известен алгоритм всех промежуточных действий и инструменты для вполнения их.</t>
+  </si>
+  <si>
+    <t>1. Собрать заявки клиента.</t>
+  </si>
+  <si>
+    <t>2. Проверить остатки товара.</t>
+  </si>
+  <si>
+    <t>??? Что дальше и каков алгоритм ???</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -224,6 +257,38 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,7 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -264,6 +329,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -493,7 +563,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -587,79 +657,84 @@
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="B22" s="3"/>
+      <c r="C22" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
@@ -4513,26 +4588,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D5D75EB-1DB7-493D-A89D-58695649C588}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -4540,15 +4615,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="I6" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -4556,57 +4634,92 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C13" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B31E73-EC71-4EBC-A252-91C0E5847F41}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4619,109 +4732,118 @@
       <c r="K5" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O5" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O7" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E5FDE9-5CCE-4EEB-B2EC-8CC075BD5DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF24475-92E5-49D4-A5CE-46580171C0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ход работы" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
   <si>
     <t>Дата1</t>
   </si>
@@ -208,6 +208,40 @@
   </si>
   <si>
     <t>??? Что дальше и каков алгоритм ???</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Решено.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Чат бот должен видеть остатки товаров в разрезе складов.</t>
+    </r>
+  </si>
+  <si>
+    <t>31 мая 2026.</t>
+  </si>
+  <si>
+    <t>SM - начало распараллеливания чатов на разные каналы - PC, WA, Web, TG.</t>
+  </si>
+  <si>
+    <t>SM - начало разбора ситуации с RAG, VectorDB - понимание смысла локументов и процессов.</t>
   </si>
 </sst>
 </file>
@@ -311,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -332,6 +366,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,12 +774,22 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="B23" s="3"/>
+      <c r="C23" s="10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="B24" s="3"/>
+      <c r="C24" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
@@ -4765,6 +4812,9 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
+      <c r="O8" s="8" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">

--- a/SMBOS_Diary.xlsx
+++ b/SMBOS_Diary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SalesmanBotOpenSource\docu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF24475-92E5-49D4-A5CE-46580171C0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35687FC-F67D-4DD7-9481-0A5EB8E50C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
   <si>
     <t>Дата1</t>
   </si>
@@ -242,6 +242,48 @@
   </si>
   <si>
     <t>SM - начало разбора ситуации с RAG, VectorDB - понимание смысла локументов и процессов.</t>
+  </si>
+  <si>
+    <t>1 июня 2026.</t>
+  </si>
+  <si>
+    <t>2 июня 2026.</t>
+  </si>
+  <si>
+    <t>3 июня 2026.</t>
+  </si>
+  <si>
+    <t>4 июня 2026.</t>
+  </si>
+  <si>
+    <t>5 июня 2026.</t>
+  </si>
+  <si>
+    <t>8 июня 2026.</t>
+  </si>
+  <si>
+    <t>WB - удачный запуск импорта из Екселя (класс ExcelReader) (пригодится для прайса). Раньше импорт из Екселя не получался.</t>
+  </si>
+  <si>
+    <t>SM - Telegram бот класс. Для тестирования  и выделения общих моментов.</t>
+  </si>
+  <si>
+    <t>SM - Telegram бот класс. Несколько вариантов.</t>
+  </si>
+  <si>
+    <t>SM - найдена и начата книга по FastAPI - основа чат-ботов.</t>
+  </si>
+  <si>
+    <t>SM - поиск вариантов внешнего облака для посадки туда чат-бота. Нужно протестировать, проблема на стороне чат-бота или же в локалке КПК.</t>
+  </si>
+  <si>
+    <t>9 июня 2026.</t>
+  </si>
+  <si>
+    <t>SM - Whatsapp чат бот, несколько вариантов. Для тестирования и выделения общих моментов.</t>
+  </si>
+  <si>
+    <t>SM - несколько вариантов класса webchattest. Второй вариант теста вызова чат бота на сайте - более наглядный.</t>
   </si>
 </sst>
 </file>
@@ -590,7 +632,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G982"/>
+  <dimension ref="A1:G976"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.85546875" style="2" customWidth="1"/>
@@ -792,32 +834,67 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="B25" s="3"/>
+      <c r="C25" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="B26" s="3"/>
+      <c r="C26" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="B27" s="3"/>
+      <c r="C27" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="B28" s="3"/>
+      <c r="C28" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="B29" s="3"/>
+      <c r="C29" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="B30" s="3"/>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
+      <c r="A31" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="B31" s="3"/>
+      <c r="C31" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
@@ -4598,30 +4675,6 @@
     <row r="976" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
-    </row>
-    <row r="977" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A977" s="3"/>
-      <c r="B977" s="3"/>
-    </row>
-    <row r="978" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A978" s="3"/>
-      <c r="B978" s="3"/>
-    </row>
-    <row r="979" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A979" s="3"/>
-      <c r="B979" s="3"/>
-    </row>
-    <row r="980" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A980" s="3"/>
-      <c r="B980" s="3"/>
-    </row>
-    <row r="981" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A981" s="3"/>
-      <c r="B981" s="3"/>
-    </row>
-    <row r="982" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A982" s="3"/>
-      <c r="B982" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
